--- a/НИРС2/hCVT model/Tmax.xlsx
+++ b/НИРС2/hCVT model/Tmax.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Баунти\Diplom\НИРС2\hCVT model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD9CF885-5E5C-432A-BF76-92AA1155E550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48973B8-A71B-4453-B2B9-43BE4AE3976C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C11D5A4F-F8E4-47B5-817F-362DC808EB68}"/>
   </bookViews>
@@ -20,116 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
-  <si>
-    <t>238,63813976751555</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 105,03597122302159</t>
-  </si>
-  <si>
-    <t>453,5745705111889</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 107,19424460431657</t>
-  </si>
-  <si>
-    <t>852,5738068762863</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 113,66906474820145</t>
-  </si>
-  <si>
-    <t>1251,5730432413843</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 120,14388489208633</t>
-  </si>
-  <si>
-    <t>1497,1866082552951</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 123,02158273381296</t>
-  </si>
-  <si>
-    <t>1988,2418087876067</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 131,29496402877697</t>
-  </si>
-  <si>
-    <t>2336,300791768819</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 133,81294964028777</t>
-  </si>
-  <si>
-    <t>2704,8193847156913</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 136,6906474820144</t>
-  </si>
-  <si>
-    <t>2991,4995377999276</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 138,1294964028777</t>
-  </si>
-  <si>
-    <t>3237,186786883343</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 139,92805755395685</t>
-  </si>
-  <si>
-    <t>3462,365303288095</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 142,0863309352518</t>
-  </si>
-  <si>
-    <t>3738,901616137257</t>
-  </si>
-  <si>
-    <t>3994,8800735947557</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 143,16546762589928</t>
-  </si>
-  <si>
-    <t>4322,7741828883245</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 141,00719424460434</t>
-  </si>
-  <si>
-    <t>4466,2125048564485</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 140,28776978417267</t>
-  </si>
-  <si>
-    <t>4732,580416114035</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 139,20863309352518</t>
-  </si>
-  <si>
-    <t>4937,49581340514</t>
-  </si>
-  <si>
-    <t>5203,91284737573</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 136,33093525179856</t>
-  </si>
-  <si>
-    <t>5490,789491311978</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 134,89208633093526</t>
-  </si>
-</sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -629,8 +520,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% — акцент1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -986,159 +878,111 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C25150E-7D1E-45AB-85E5-A24C35F861D4}">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+      <c r="A1" s="1">
+        <v>600</v>
+      </c>
+      <c r="B1" s="1">
+        <v>101.098901098901</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
+      <c r="A2" s="1">
+        <v>941.88034188034101</v>
+      </c>
+      <c r="B2" s="1">
+        <v>106.593406593406</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
+      <c r="A3" s="1">
+        <v>1488.88888888888</v>
+      </c>
+      <c r="B3" s="1">
+        <v>116.483516483516</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
+      <c r="A4" s="1">
+        <v>1926.49572649572</v>
+      </c>
+      <c r="B4" s="1">
+        <v>123.07692307692299</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
+      <c r="A5" s="1">
+        <v>2350.4273504273501</v>
+      </c>
+      <c r="B5" s="1">
+        <v>131.318681318681</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
+      <c r="A6" s="1">
+        <v>3006.8376068376001</v>
+      </c>
+      <c r="B6" s="1">
+        <v>136.81318681318601</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
+      <c r="A7" s="1">
+        <v>3252.9914529914499</v>
+      </c>
+      <c r="B7" s="1">
+        <v>138.461538461538</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
+      <c r="A8" s="1">
+        <v>3663.2478632478601</v>
+      </c>
+      <c r="B8" s="1">
+        <v>141.75824175824101</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
+      <c r="A9" s="1">
+        <v>4100.8547008547002</v>
+      </c>
+      <c r="B9" s="1">
+        <v>142.85714285714201</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
+      <c r="A10" s="1">
+        <v>4497.4358974358902</v>
+      </c>
+      <c r="B10" s="1">
+        <v>140.10989010988999</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
+      <c r="A11" s="1">
+        <v>4839.3162393162302</v>
+      </c>
+      <c r="B11" s="1">
+        <v>137.912087912087</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>21</v>
+      <c r="A12" s="1">
+        <v>5167.5213675213599</v>
+      </c>
+      <c r="B12" s="1">
+        <v>136.26373626373601</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" t="s">
-        <v>35</v>
+      <c r="A13" s="1">
+        <v>5413.6752136752102</v>
+      </c>
+      <c r="B13" s="1">
+        <v>134.06593406593399</v>
       </c>
     </row>
   </sheetData>

--- a/НИРС2/hCVT model/Tmax.xlsx
+++ b/НИРС2/hCVT model/Tmax.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Баунти\Diplom\НИРС2\hCVT model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48973B8-A71B-4453-B2B9-43BE4AE3976C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98B4E50-D266-4ACD-BCE7-7C72F6E4CD12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C11D5A4F-F8E4-47B5-817F-362DC808EB68}"/>
   </bookViews>
@@ -17,10 +17,6 @@
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -880,6 +876,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C25150E-7D1E-45AB-85E5-A24C35F861D4}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.81640625" style="1" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1">
@@ -979,7 +979,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
-        <v>5413.6752136752102</v>
+        <v>5400</v>
       </c>
       <c r="B13" s="1">
         <v>134.06593406593399</v>

--- a/НИРС2/hCVT model/Tmax.xlsx
+++ b/НИРС2/hCVT model/Tmax.xlsx
@@ -1,21 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Баунти\Diplom\НИРС2\hCVT model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98B4E50-D266-4ACD-BCE7-7C72F6E4CD12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A914700-85BF-4711-B55B-464FC2B9D80E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C11D5A4F-F8E4-47B5-817F-362DC808EB68}"/>
   </bookViews>
   <sheets>
     <sheet name="Tmax" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -883,7 +894,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="B1" s="1">
         <v>101.098901098901</v>
@@ -891,7 +902,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
-        <v>941.88034188034101</v>
+        <v>1113.3903133903127</v>
       </c>
       <c r="B2" s="1">
         <v>106.593406593406</v>
@@ -899,7 +910,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
-        <v>1488.88888888888</v>
+        <v>1614.8148148148068</v>
       </c>
       <c r="B3" s="1">
         <v>116.483516483516</v>
@@ -907,7 +918,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
-        <v>1926.49572649572</v>
+        <v>2015.95441595441</v>
       </c>
       <c r="B4" s="1">
         <v>123.07692307692299</v>
@@ -915,7 +926,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
-        <v>2350.4273504273501</v>
+        <v>2404.5584045584042</v>
       </c>
       <c r="B5" s="1">
         <v>131.318681318681</v>
@@ -923,7 +934,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
-        <v>3006.8376068376001</v>
+        <v>3006.2678062678001</v>
       </c>
       <c r="B6" s="1">
         <v>136.81318681318601</v>
@@ -931,7 +942,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
-        <v>3252.9914529914499</v>
+        <v>3231.9088319088291</v>
       </c>
       <c r="B7" s="1">
         <v>138.461538461538</v>
@@ -939,7 +950,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
-        <v>3663.2478632478601</v>
+        <v>3607.9772079772051</v>
       </c>
       <c r="B8" s="1">
         <v>141.75824175824101</v>
@@ -947,7 +958,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
-        <v>4100.8547008547002</v>
+        <v>4009.1168091168088</v>
       </c>
       <c r="B9" s="1">
         <v>142.85714285714201</v>
@@ -955,7 +966,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
-        <v>4497.4358974358902</v>
+        <v>4372.6495726495659</v>
       </c>
       <c r="B10" s="1">
         <v>140.10989010988999</v>
@@ -963,7 +974,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
-        <v>4839.3162393162302</v>
+        <v>4686.0398860398773</v>
       </c>
       <c r="B11" s="1">
         <v>137.912087912087</v>
@@ -971,7 +982,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
-        <v>5167.5213675213599</v>
+        <v>4986.8945868945802</v>
       </c>
       <c r="B12" s="1">
         <v>136.26373626373601</v>
@@ -979,7 +990,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
-        <v>5400</v>
+        <v>5200</v>
       </c>
       <c r="B13" s="1">
         <v>134.06593406593399</v>
